--- a/batch_experiments/2026_02_04/T3600/V5_02/scores_summary.xlsx
+++ b/batch_experiments/2026_02_04/T3600/V5_02/scores_summary.xlsx
@@ -967,7 +967,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -977,7 +977,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>OPTIMAL</t>
+          <t>FEASIBLE</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>OPTIMAL</t>
+          <t>FEASIBLE</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>OPTIMAL</t>
+          <t>FEASIBLE</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>OPTIMAL</t>
+          <t>FEASIBLE</t>
         </is>
       </c>
     </row>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>OPTIMAL</t>
+          <t>FEASIBLE</t>
         </is>
       </c>
     </row>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>OPTIMAL</t>
+          <t>FEASIBLE</t>
         </is>
       </c>
     </row>
@@ -1157,7 +1157,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>OPTIMAL</t>
+          <t>FEASIBLE</t>
         </is>
       </c>
     </row>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>OPTIMAL</t>
+          <t>FEASIBLE</t>
         </is>
       </c>
     </row>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>OPTIMAL</t>
+          <t>FEASIBLE</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>OPTIMAL</t>
+          <t>FEASIBLE</t>
         </is>
       </c>
     </row>
